--- a/diseases/d085/2026-2029.xlsx
+++ b/diseases/d085/2026-2029.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2163299454776194</v>
+        <v>0.2156742412565021</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-AC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Acre, Brazil</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -908,20 +908,17 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.7884711993998608</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -950,42 +947,33 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1005,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BR-AL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Alagoas, Brazil</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,29 +1035,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0632132957564472</v>
+        <v>0.5588104539776129</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1098,42 +1083,33 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1141,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-AM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Amazonas, Brazil</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1195,29 +1171,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.5503418310698233</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1246,42 +1219,33 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1277,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-AP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Amapá, Brazil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1343,29 +1307,26 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.6173197704064309</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1394,42 +1355,33 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1413,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-BA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Bahia, Brazil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1491,26 +1443,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.1276069426773495</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1539,42 +1491,33 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1549,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-CE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Ceará, Brazil</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1636,26 +1579,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.1397517213918282</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1684,42 +1627,33 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1685,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR-DF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Distrito Federal, Brazil</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1781,26 +1715,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.1993358130708479</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1829,40 +1763,7450 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BR-ES</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Espírito Santo, Brazil</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.07227710463700993</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BR-GO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goiás, Brazil</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1467638634813216</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BR-MA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maranhão, Brazil</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.213536597396818</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.111834353192738</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BR-MT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mato Grosso, Brazil</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3797151124083304</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pará, Brazil</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.07994222232982699</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BR-PB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paraíba, Brazil</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4781454078436885</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pernambuco, Brazil</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2608738480854364</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BR-PI</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Piauí, Brazil</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2947577047453338</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BR-PR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paraná, Brazil</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2091620333093048</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>19</v>
+      </c>
+      <c r="O21" t="n">
+        <v>19</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1103021640704053</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BR-RN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte, Brazil</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>14</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4041877313433439</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BR-RO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rondônia, Brazil</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1707127484866315</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BR-RR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Roraima, Brazil</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1314039726048998</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>37</v>
+      </c>
+      <c r="O25" t="n">
+        <v>37</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3293773335160042</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Santa Catarina, Brazil</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>19</v>
+      </c>
+      <c r="O26" t="n">
+        <v>19</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2285643069888108</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BR-SE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sergipe, Brazil</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>68</v>
+      </c>
+      <c r="O27" t="n">
+        <v>68</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.947225165835593</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>44</v>
+      </c>
+      <c r="O28" t="n">
+        <v>44</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.09528138846118132</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BR-TO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tocantins, Brazil</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.6265687715617979</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AW30" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BB30" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>135</v>
+      </c>
+      <c r="O31" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.06302169387365321</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BR-AC</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Acre, Brazil</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.1126387427714087</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BR-AL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alagoas, Brazil</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.09313507566293547</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BR-AM</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Amazonas, Brazil</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.1375854577674558</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>BR-AP</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Amapá, Brazil</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BR-BA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bahia, Brazil</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.02686461951102094</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BR-CE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ceará, Brazil</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.04300052965902407</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.06644527102361598</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BR-ES</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Espírito Santo, Brazil</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BR-GO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goiás, Brazil</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" t="n">
+        <v>8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.1067373552591429</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BR-MA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Maranhão, Brazil</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>14</v>
+      </c>
+      <c r="O41" t="n">
+        <v>14</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.1993008242370302</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.02795858829818449</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BR-MT</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Mato Grosso, Brazil</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.05062868165444406</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pará, Brazil</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.04568126990275828</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BR-PB</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Paraíba, Brazil</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>8</v>
+      </c>
+      <c r="O46" t="n">
+        <v>8</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.1912581631374754</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pernambuco, Brazil</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>6</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.06260972354050473</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BR-PI</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Piauí, Brazil</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BR-PR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Paraná, Brazil</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>10</v>
+      </c>
+      <c r="O49" t="n">
+        <v>10</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.08366481332372191</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.00580537705633712</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BR-RN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte, Brazil</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.02887055223881028</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BR-RO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rondônia, Brazil</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.05690424949554383</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BR-RR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Roraima, Brazil</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>6</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.7884238356293988</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>16</v>
+      </c>
+      <c r="O54" t="n">
+        <v>16</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.1424334415204342</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Santa Catarina, Brazil</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.08420790257482504</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BR-SE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sergipe, Brazil</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.3033908258948404</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>12</v>
+      </c>
+      <c r="O57" t="n">
+        <v>12</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.02598583321668582</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BR-TO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tocantins, Brazil</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.3759412629370787</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.008691384892873792</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1984,7 +9328,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1994,7 +9338,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -2046,7 +9390,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>607</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d085/2026-2029.xlsx
+++ b/diseases/d085/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1193,6 +1208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1329,6 +1349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1601,6 +1631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1737,6 +1772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1873,6 +1913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2145,6 +2195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2281,6 +2336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2417,6 +2477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2553,6 +2618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2689,6 +2759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2961,6 +3041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3097,6 +3182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3233,6 +3323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3369,6 +3464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3505,6 +3605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3641,6 +3746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3913,6 +4028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4049,6 +4169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4185,6 +4310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4321,6 +4451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4457,6 +4592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4596,6 +4736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4744,6 +4889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4889,6 +5039,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5025,6 +5180,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5161,6 +5321,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5297,6 +5462,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5433,6 +5603,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5569,6 +5744,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5705,6 +5885,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5841,6 +6026,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5977,6 +6167,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6113,6 +6308,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6249,6 +6449,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6385,6 +6590,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6521,6 +6731,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6657,6 +6872,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6793,6 +7013,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6929,6 +7154,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7065,6 +7295,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7201,6 +7436,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7337,6 +7577,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7473,6 +7718,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7609,6 +7859,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7745,6 +8000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7881,6 +8141,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8017,6 +8282,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8153,6 +8423,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8289,6 +8564,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8425,6 +8705,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8564,6 +8849,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8712,6 +9002,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8857,6 +9152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9002,6 +9302,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9145,6 +9450,11 @@
       <c r="S63" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">

--- a/diseases/d085/2026-2029.xlsx
+++ b/diseases/d085/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.2156742412565021</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.7884711993998608</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,23 +918,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1062,11 +1032,6 @@
       <c r="R4" t="n">
         <v>0.5588104539776129</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1079,23 +1044,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1203,11 +1158,6 @@
       <c r="R5" t="n">
         <v>0.5503418310698233</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1220,23 +1170,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1344,11 +1284,6 @@
       <c r="R6" t="n">
         <v>0.6173197704064309</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1361,23 +1296,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1485,11 +1410,6 @@
       <c r="R7" t="n">
         <v>0.1276069426773495</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1502,23 +1422,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1626,11 +1536,6 @@
       <c r="R8" t="n">
         <v>0.1397517213918282</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1643,23 +1548,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1767,11 +1662,6 @@
       <c r="R9" t="n">
         <v>0.1993358130708479</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1784,23 +1674,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1908,11 +1788,6 @@
       <c r="R10" t="n">
         <v>0.07227710463700993</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1925,23 +1800,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -2049,11 +1914,6 @@
       <c r="R11" t="n">
         <v>0.1467638634813216</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2066,23 +1926,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2190,11 +2040,6 @@
       <c r="R12" t="n">
         <v>0.213536597396818</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2207,23 +2052,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2331,11 +2166,6 @@
       <c r="R13" t="n">
         <v>0.111834353192738</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2348,23 +2178,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2472,11 +2292,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2489,23 +2304,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2613,11 +2418,6 @@
       <c r="R15" t="n">
         <v>0.3797151124083304</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2630,23 +2430,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2754,11 +2544,6 @@
       <c r="R16" t="n">
         <v>0.07994222232982699</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2771,23 +2556,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2895,11 +2670,6 @@
       <c r="R17" t="n">
         <v>0.4781454078436885</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2912,23 +2682,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -3036,11 +2796,6 @@
       <c r="R18" t="n">
         <v>0.2608738480854364</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3053,23 +2808,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3177,11 +2922,6 @@
       <c r="R19" t="n">
         <v>0.2947577047453338</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3194,23 +2934,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3318,11 +3048,6 @@
       <c r="R20" t="n">
         <v>0.2091620333093048</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,23 +3060,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3459,11 +3174,6 @@
       <c r="R21" t="n">
         <v>0.1103021640704053</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3476,23 +3186,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3600,11 +3300,6 @@
       <c r="R22" t="n">
         <v>0.4041877313433439</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3617,23 +3312,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3741,11 +3426,6 @@
       <c r="R23" t="n">
         <v>0.1707127484866315</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3758,23 +3438,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3882,11 +3552,6 @@
       <c r="R24" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3899,23 +3564,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -4023,11 +3678,6 @@
       <c r="R25" t="n">
         <v>0.3293773335160042</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4040,23 +3690,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -4164,11 +3804,6 @@
       <c r="R26" t="n">
         <v>0.2285643069888108</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4181,23 +3816,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4305,11 +3930,6 @@
       <c r="R27" t="n">
         <v>2.947225165835593</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4322,23 +3942,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4446,11 +4056,6 @@
       <c r="R28" t="n">
         <v>0.09528138846118132</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4463,23 +4068,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4587,11 +4182,6 @@
       <c r="R29" t="n">
         <v>0.6265687715617979</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4604,23 +4194,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4731,11 +4311,6 @@
       <c r="R30" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4748,23 +4323,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4884,11 +4449,6 @@
       <c r="R31" t="n">
         <v>0.06302169387365321</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4901,23 +4461,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -5034,11 +4584,6 @@
       <c r="R32" t="n">
         <v>0.1126387427714087</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5051,23 +4596,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -5175,11 +4710,6 @@
       <c r="R33" t="n">
         <v>0.09313507566293547</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5192,23 +4722,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5316,11 +4836,6 @@
       <c r="R34" t="n">
         <v>0.1375854577674558</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5333,23 +4848,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5457,11 +4962,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5474,23 +4974,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5598,11 +5088,6 @@
       <c r="R36" t="n">
         <v>0.02686461951102094</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5615,23 +5100,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5739,11 +5214,6 @@
       <c r="R37" t="n">
         <v>0.04300052965902407</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5756,23 +5226,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5880,11 +5340,6 @@
       <c r="R38" t="n">
         <v>0.06644527102361598</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5897,23 +5352,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -6021,11 +5466,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6038,23 +5478,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -6162,11 +5592,6 @@
       <c r="R40" t="n">
         <v>0.1067373552591429</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6179,23 +5604,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6303,11 +5718,6 @@
       <c r="R41" t="n">
         <v>0.1993008242370302</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6320,23 +5730,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6444,11 +5844,6 @@
       <c r="R42" t="n">
         <v>0.02795858829818449</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6461,23 +5856,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6585,11 +5970,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,23 +5982,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6726,11 +6096,6 @@
       <c r="R44" t="n">
         <v>0.05062868165444406</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6743,23 +6108,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6867,11 +6222,6 @@
       <c r="R45" t="n">
         <v>0.04568126990275828</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6884,23 +6234,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -7008,11 +6348,6 @@
       <c r="R46" t="n">
         <v>0.1912581631374754</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7025,23 +6360,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -7149,11 +6474,6 @@
       <c r="R47" t="n">
         <v>0.06260972354050473</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7166,23 +6486,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -7290,11 +6600,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7307,23 +6612,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7431,11 +6726,6 @@
       <c r="R49" t="n">
         <v>0.08366481332372191</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7448,23 +6738,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7572,11 +6852,6 @@
       <c r="R50" t="n">
         <v>0.00580537705633712</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7589,23 +6864,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -7713,11 +6978,6 @@
       <c r="R51" t="n">
         <v>0.02887055223881028</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7730,23 +6990,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7854,11 +7104,6 @@
       <c r="R52" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7871,23 +7116,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7995,11 +7230,6 @@
       <c r="R53" t="n">
         <v>0.7884238356293988</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8012,23 +7242,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -8136,11 +7356,6 @@
       <c r="R54" t="n">
         <v>0.1424334415204342</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8153,23 +7368,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -8277,11 +7482,6 @@
       <c r="R55" t="n">
         <v>0.08420790257482504</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8294,23 +7494,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8418,11 +7608,6 @@
       <c r="R56" t="n">
         <v>0.3033908258948404</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8435,23 +7620,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8559,11 +7734,6 @@
       <c r="R57" t="n">
         <v>0.02598583321668582</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8576,23 +7746,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8700,11 +7860,6 @@
       <c r="R58" t="n">
         <v>0.3759412629370787</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8717,23 +7872,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -8844,11 +7989,6 @@
       <c r="R59" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8861,23 +8001,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -8942,17 +8072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8991,130 +8121,34 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="P60" t="n">
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
         <v>1</v>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -9127,12 +8161,12 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -9147,12 +8181,12 @@
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9184,12 +8218,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9214,101 +8248,83 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.01738276978574758</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9335,7 +8351,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -9370,12 +8386,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9389,94 +8405,11 @@
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN62" t="b">
-        <v>1</v>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9484,12 +8417,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9499,11 +8427,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9574,12 +8497,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9604,98 +8527,86 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9722,17 +8633,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9757,12 +8668,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -9771,168 +8682,66 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
+      <c r="R64" t="n">
+        <v>0.004345692446436896</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN64" t="b">
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT64" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9994,12 +8803,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10008,11 +8817,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
@@ -10030,12 +8834,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -10045,11 +8844,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10115,17 +8909,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10150,179 +8944,80 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.008691384892873792</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN66" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10349,17 +9044,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10384,182 +9079,80 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.004345692446436896</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10621,24 +9214,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10657,12 +9245,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10672,11 +9255,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10742,17 +9320,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10777,113 +9355,33 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.001195539327995473</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -10891,12 +9389,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -10907,11 +9400,6 @@
       <c r="AT69" t="n">
         <v>1</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -10924,12 +9412,12 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
@@ -10944,12 +9432,12 @@
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -10981,12 +9469,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11011,12 +9499,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11025,2491 +9513,70 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="R70" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP71" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT71" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV71" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA71" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB71" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="BC71" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV72" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA72" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB72" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC72" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA73" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB73" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC73" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Taiwan, China</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>2</v>
-      </c>
-      <c r="O74" t="n">
-        <v>2</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP74" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
-      <c r="AT74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV74" t="inlineStr">
-        <is>
-          <t>nidss_open_data</t>
-        </is>
-      </c>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>nidss_open_data</t>
-        </is>
-      </c>
-      <c r="BA74" t="inlineStr">
-        <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB74" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
-      <c r="BC74" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Taiwan, China</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP75" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
-      <c r="AT75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV75" t="inlineStr">
-        <is>
-          <t>nidss_open_data</t>
-        </is>
-      </c>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>nidss_open_data</t>
-        </is>
-      </c>
-      <c r="BA75" t="inlineStr">
-        <is>
-          <t>Taiwan, China CDC NIDSS</t>
-        </is>
-      </c>
-      <c r="BB75" t="inlineStr">
-        <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
-        </is>
-      </c>
-      <c r="BC75" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT76" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA76" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB76" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="BC76" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT77" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV77" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA77" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB77" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="BC77" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP78" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV78" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA78" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB78" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC78" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV79" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA79" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB79" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC79" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP80" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT80" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV80" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA80" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB80" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="BC80" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV81" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA81" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB81" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC81" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>toxoplasmose</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Toxoplasmose</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV82" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA82" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB82" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC82" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -13631,7 +9698,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -13641,7 +9708,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -13661,7 +9728,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13671,7 +9738,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13693,7 +9760,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d085/2026-2029.xlsx
+++ b/diseases/d085/2026-2029.xlsx
@@ -8072,17 +8072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8121,33 +8121,134 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8161,12 +8262,12 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -8181,12 +8282,12 @@
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8319,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8248,83 +8349,101 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.01738276978574758</v>
+        <v>1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8470,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8386,12 +8505,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -8405,11 +8524,94 @@
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -8417,7 +8619,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -8427,6 +8634,11 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -8497,12 +8709,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8527,33 +8739,34 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.01738276978574758</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
@@ -8561,52 +8774,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8633,17 +8842,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8668,12 +8877,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -8682,66 +8891,173 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="R64" t="n">
-        <v>0.004345692446436896</v>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN64" t="b">
+        <v>0</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -8803,12 +9119,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -8817,6 +9133,11 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
@@ -8834,7 +9155,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -8844,6 +9170,11 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -8909,17 +9240,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8944,80 +9275,179 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.008691384892873792</v>
+        <v>1</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9044,17 +9474,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -9079,80 +9509,187 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.004345692446436896</v>
+        <v>2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>0</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -9214,19 +9751,24 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -9245,7 +9787,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -9255,6 +9802,11 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9320,17 +9872,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9355,33 +9907,113 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
         <v>1</v>
       </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.001195539327995473</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9389,7 +10021,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -9400,6 +10037,11 @@
       <c r="AT69" t="n">
         <v>1</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -9412,12 +10054,12 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
@@ -9432,12 +10074,12 @@
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9469,12 +10111,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9499,12 +10141,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -9513,70 +10155,2869 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="R70" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
         <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AT71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP70" t="inlineStr">
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.008691384892873792</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
-      <c r="AT70" t="n">
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
         <v>1</v>
       </c>
-      <c r="AV70" t="inlineStr">
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="AW70" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
+      <c r="AY78" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="BA70" t="inlineStr">
+      <c r="BA78" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="BB70" t="inlineStr">
+      <c r="BB78" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
-      <c r="BC70" t="inlineStr">
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>sha256:ad75b8bc0e9221501c8dbe115fd759f7b46141decfccf733c7ed792af01c24f5</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>toxoplasmose</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Toxoplasmose</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -9708,7 +13149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -9728,7 +13169,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -9738,7 +13179,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d085/2026-2029.xlsx
+++ b/diseases/d085/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.2156742412565021</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0.7884711993998608</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,13 +938,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -935,6 +965,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>web</t>
@@ -950,7 +985,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC3" t="inlineStr">
         <is>
           <t>web</t>
@@ -1032,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0.5588104539776129</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1044,13 +1088,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1061,6 +1115,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1076,7 +1135,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1158,6 +1221,11 @@
       <c r="R5" t="n">
         <v>0.5503418310698233</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1170,13 +1238,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1187,6 +1265,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1202,7 +1285,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1284,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0.6173197704064309</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1296,13 +1388,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1313,6 +1415,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1328,7 +1435,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1410,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0.1276069426773495</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1422,13 +1538,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1439,6 +1565,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1454,7 +1585,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1536,6 +1671,11 @@
       <c r="R8" t="n">
         <v>0.1397517213918282</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1548,13 +1688,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1565,6 +1715,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1580,7 +1735,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1662,6 +1821,11 @@
       <c r="R9" t="n">
         <v>0.1993358130708479</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1674,13 +1838,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1691,6 +1865,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1706,7 +1885,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1788,6 +1971,11 @@
       <c r="R10" t="n">
         <v>0.07227710463700993</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1800,13 +1988,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -1817,6 +2015,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1832,7 +2035,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1914,6 +2121,11 @@
       <c r="R11" t="n">
         <v>0.1467638634813216</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1926,13 +2138,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -1943,6 +2165,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>web</t>
@@ -1958,7 +2185,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC11" t="inlineStr">
         <is>
           <t>web</t>
@@ -2040,6 +2271,11 @@
       <c r="R12" t="n">
         <v>0.213536597396818</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2052,13 +2288,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2069,6 +2315,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2084,7 +2335,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2166,6 +2421,11 @@
       <c r="R13" t="n">
         <v>0.111834353192738</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2178,13 +2438,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2195,6 +2465,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2210,7 +2485,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2292,6 +2571,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2304,13 +2588,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2321,6 +2615,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2336,7 +2635,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2418,6 +2721,11 @@
       <c r="R15" t="n">
         <v>0.3797151124083304</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2430,13 +2738,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2447,6 +2765,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2462,7 +2785,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2544,6 +2871,11 @@
       <c r="R16" t="n">
         <v>0.07994222232982699</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2556,13 +2888,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2573,6 +2915,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2588,7 +2935,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2670,6 +3021,11 @@
       <c r="R17" t="n">
         <v>0.4781454078436885</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2682,13 +3038,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2699,6 +3065,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2714,7 +3085,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2796,6 +3171,11 @@
       <c r="R18" t="n">
         <v>0.2608738480854364</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2808,13 +3188,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -2825,6 +3215,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2840,7 +3235,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2922,6 +3321,11 @@
       <c r="R19" t="n">
         <v>0.2947577047453338</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2934,13 +3338,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -2951,6 +3365,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
@@ -2966,7 +3385,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3048,6 +3471,11 @@
       <c r="R20" t="n">
         <v>0.2091620333093048</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3060,13 +3488,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3077,6 +3515,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3092,7 +3535,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3174,6 +3621,11 @@
       <c r="R21" t="n">
         <v>0.1103021640704053</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3186,13 +3638,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3203,6 +3665,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3218,7 +3685,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3300,6 +3771,11 @@
       <c r="R22" t="n">
         <v>0.4041877313433439</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3312,13 +3788,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3329,6 +3815,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3344,7 +3835,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3426,6 +3921,11 @@
       <c r="R23" t="n">
         <v>0.1707127484866315</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3438,13 +3938,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3455,6 +3965,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3470,7 +3985,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3552,6 +4071,11 @@
       <c r="R24" t="n">
         <v>0.1314039726048998</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3564,13 +4088,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3581,6 +4115,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3596,7 +4135,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3678,6 +4221,11 @@
       <c r="R25" t="n">
         <v>0.3293773335160042</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3690,13 +4238,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3707,6 +4265,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3722,7 +4285,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3804,6 +4371,11 @@
       <c r="R26" t="n">
         <v>0.2285643069888108</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3816,13 +4388,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -3833,6 +4415,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3848,7 +4435,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3930,6 +4521,11 @@
       <c r="R27" t="n">
         <v>2.947225165835593</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3942,13 +4538,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -3959,6 +4565,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
@@ -3974,7 +4585,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4056,6 +4671,11 @@
       <c r="R28" t="n">
         <v>0.09528138846118132</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4068,13 +4688,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4085,6 +4715,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4100,7 +4735,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4182,6 +4821,11 @@
       <c r="R29" t="n">
         <v>0.6265687715617979</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4194,13 +4838,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4211,6 +4865,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4226,7 +4885,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4449,6 +5112,11 @@
       <c r="R31" t="n">
         <v>0.06302169387365321</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4461,13 +5129,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -4584,6 +5262,11 @@
       <c r="R32" t="n">
         <v>0.1126387427714087</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4596,13 +5279,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4613,6 +5306,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4628,7 +5326,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4710,6 +5412,11 @@
       <c r="R33" t="n">
         <v>0.09313507566293547</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4722,13 +5429,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -4739,6 +5456,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4754,7 +5476,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4836,6 +5562,11 @@
       <c r="R34" t="n">
         <v>0.1375854577674558</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4848,13 +5579,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -4865,6 +5606,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4880,7 +5626,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4962,6 +5712,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4974,13 +5729,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -4991,6 +5756,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5006,7 +5776,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5088,6 +5862,11 @@
       <c r="R36" t="n">
         <v>0.02686461951102094</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5100,13 +5879,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5117,6 +5906,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5132,7 +5926,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5214,6 +6012,11 @@
       <c r="R37" t="n">
         <v>0.04300052965902407</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5226,13 +6029,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5243,6 +6056,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5258,7 +6076,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5340,6 +6162,11 @@
       <c r="R38" t="n">
         <v>0.06644527102361598</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5352,13 +6179,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5369,6 +6206,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5384,7 +6226,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5466,6 +6312,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5478,13 +6329,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5495,6 +6356,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5510,7 +6376,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5592,6 +6462,11 @@
       <c r="R40" t="n">
         <v>0.1067373552591429</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5604,13 +6479,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -5621,6 +6506,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5636,7 +6526,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5718,6 +6612,11 @@
       <c r="R41" t="n">
         <v>0.1993008242370302</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5730,13 +6629,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -5747,6 +6656,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5762,7 +6676,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5844,6 +6762,11 @@
       <c r="R42" t="n">
         <v>0.02795858829818449</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5856,13 +6779,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -5873,6 +6806,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>web</t>
@@ -5888,7 +6826,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
@@ -5970,6 +6912,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5982,13 +6929,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -5999,6 +6956,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6014,7 +6976,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6096,6 +7062,11 @@
       <c r="R44" t="n">
         <v>0.05062868165444406</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6108,13 +7079,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6125,6 +7106,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6140,7 +7126,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6222,6 +7212,11 @@
       <c r="R45" t="n">
         <v>0.04568126990275828</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6234,13 +7229,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6251,6 +7256,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6266,7 +7276,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6348,6 +7362,11 @@
       <c r="R46" t="n">
         <v>0.1912581631374754</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6360,13 +7379,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -6377,6 +7406,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6392,7 +7426,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6474,6 +7512,11 @@
       <c r="R47" t="n">
         <v>0.06260972354050473</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6486,13 +7529,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -6503,6 +7556,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6518,7 +7576,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6600,6 +7662,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6612,13 +7679,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -6629,6 +7706,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6644,7 +7726,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6726,6 +7812,11 @@
       <c r="R49" t="n">
         <v>0.08366481332372191</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6738,13 +7829,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -6755,6 +7856,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6770,7 +7876,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6852,6 +7962,11 @@
       <c r="R50" t="n">
         <v>0.00580537705633712</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6864,13 +7979,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -6881,6 +8006,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>web</t>
@@ -6896,7 +8026,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC50" t="inlineStr">
         <is>
           <t>web</t>
@@ -6978,6 +8112,11 @@
       <c r="R51" t="n">
         <v>0.02887055223881028</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6990,13 +8129,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7007,6 +8156,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7022,7 +8176,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7104,6 +8262,11 @@
       <c r="R52" t="n">
         <v>0.05690424949554383</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7116,13 +8279,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7133,6 +8306,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7148,7 +8326,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7230,6 +8412,11 @@
       <c r="R53" t="n">
         <v>0.7884238356293988</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7242,13 +8429,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -7259,6 +8456,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7274,7 +8476,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7356,6 +8562,11 @@
       <c r="R54" t="n">
         <v>0.1424334415204342</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7368,13 +8579,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7385,6 +8606,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7400,7 +8626,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7482,6 +8712,11 @@
       <c r="R55" t="n">
         <v>0.08420790257482504</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7494,13 +8729,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -7511,6 +8756,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7526,7 +8776,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7608,6 +8862,11 @@
       <c r="R56" t="n">
         <v>0.3033908258948404</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7620,13 +8879,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -7637,6 +8906,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7652,7 +8926,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7734,6 +9012,11 @@
       <c r="R57" t="n">
         <v>0.02598583321668582</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7746,13 +9029,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -7763,6 +9056,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>web</t>
@@ -7778,7 +9076,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
@@ -7860,6 +9162,11 @@
       <c r="R58" t="n">
         <v>0.3759412629370787</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7872,13 +9179,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -7889,6 +9206,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>web</t>
@@ -7904,7 +9226,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC58" t="inlineStr">
         <is>
           <t>web</t>
